--- a/排课结果/特殊要求放宽排入明细.xlsx
+++ b/排课结果/特殊要求放宽排入明细.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,45 +424,50 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>虚班</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>课程名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>教师号</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>周学时</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>教室代码</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>教室</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>节次</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>周次数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>放宽桶</t>
         </is>
@@ -474,43 +479,44 @@
           <t>150000290.015</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>xkp01120077</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>CLS1315</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>乒乓球训练房1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>18</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -522,43 +528,44 @@
           <t>150000290.061</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>xkp01050012</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>CLS1316</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>乒乓球训练房2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>18</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -570,43 +577,44 @@
           <t>150000290.062</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>xkp01231168</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>18</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -618,43 +626,44 @@
           <t>150000290.063</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>xkp01050013</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>CLS1318</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>武术训练房2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>18</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -666,43 +675,44 @@
           <t>150000290.064</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>xkp01050062</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>CLS1319</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>舞操训练房1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>18</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -714,43 +724,44 @@
           <t>150000290.066</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>xkp01050070</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>CLS1320</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>舞操训练房2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>18</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -762,43 +773,44 @@
           <t>150000290.068</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>xkp01231126</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>CLS1321</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>健身实训中心</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>18</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -810,43 +822,44 @@
           <t>150000290.069</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>xkp01230328</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>CLS1333</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>东区足球2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>18</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -858,43 +871,44 @@
           <t>150000290.071</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>xkp01050017</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>CLS1334</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>东区排球1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>18</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -906,43 +920,44 @@
           <t>150000290.073</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>xkp01230344</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>CLS1335</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>东区排球2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>18</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -954,43 +969,44 @@
           <t>150000290.088</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>xkp01230344</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>CLS1316</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>乒乓球训练房2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>18</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1002,43 +1018,44 @@
           <t>150000290.089</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>xkp01230939</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>CLS1318</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>武术训练房2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>18</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1050,43 +1067,44 @@
           <t>150000290.090</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>xkp01050058</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>CLS1319</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>舞操训练房1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>18</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1098,43 +1116,44 @@
           <t>150000290.093</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>xkp01050004</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>CLS1320</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>舞操训练房2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>18</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1146,43 +1165,44 @@
           <t>150000290.095</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>xkp01231168</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>CLS1331</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>乒乓球训练房3</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>18</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1194,43 +1214,44 @@
           <t>150000290.097</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>xkp01050070</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>CLS1332</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>东区足球1</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>18</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1242,43 +1263,44 @@
           <t>150000290.098</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>xkp01050014</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>CLS1315</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>乒乓球训练房1</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>周五</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>18</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1290,43 +1312,44 @@
           <t>150000290.099</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>xkp01231126</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>CLS1316</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>乒乓球训练房2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>周五</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>18</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1338,43 +1361,44 @@
           <t>150000290.100</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>xkp01050084</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>周五</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>18</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1386,43 +1410,44 @@
           <t>150000290.101</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>xkp01050008</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>CLS1318</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>武术训练房2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>周五</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>18</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1434,43 +1459,44 @@
           <t>150000290.223</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>xkp01050063</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>CLS1316</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>乒乓球训练房2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>18</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1482,43 +1508,44 @@
           <t>150000290.227</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
         <is>
           <t>体育与健康4</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>xkp01231163</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>CLS1336</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>东区排球3</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>18</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1530,43 +1557,44 @@
           <t>15200002.014</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>xkp01960015</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>CLS1333</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>东区足球2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>18</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1578,43 +1606,44 @@
           <t>15200002.015</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>xkp01050038</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>CLS1333</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>东区足球2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>18</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1626,43 +1655,44 @@
           <t>15200002.016</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>xkp01050022</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>CLS1333</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>东区足球2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>18</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1674,43 +1704,44 @@
           <t>15200002.019</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>xkp01050028</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>CLS1510</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>舞操训练房</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>18</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1722,43 +1753,44 @@
           <t>15200002.024</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>xkp01050006</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>CLS1333</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>东区足球2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>18</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1770,43 +1802,44 @@
           <t>15200002.050</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>xkp01050006</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>18</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1818,43 +1851,44 @@
           <t>15200002.051</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>xkp01050049</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>18</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1866,43 +1900,44 @@
           <t>15200002.053</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>xkp01050050</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>18</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1914,43 +1949,44 @@
           <t>15200002.055</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>xkp01050066</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>18</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1962,43 +1998,44 @@
           <t>15200002.056</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>xkp01050042</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>18</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2010,43 +2047,44 @@
           <t>15200002.057</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>xkp01050046</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>18</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2058,43 +2096,44 @@
           <t>15200002.058</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>xkp01050033</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>18</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2106,43 +2145,44 @@
           <t>15200002.059</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>xkp01050010</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>18</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2154,43 +2194,44 @@
           <t>15200002.060</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>xkp01230625</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>18</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2202,43 +2243,44 @@
           <t>15200002.061</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>xkp01050075</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>CLS1317</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>武术训练房1</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>18</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2250,43 +2292,44 @@
           <t>15200002.062</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>xkp01170079</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>CLS1509</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>健身房</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>18</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2298,43 +2341,44 @@
           <t>15200002.063</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>xkp01170064</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>CLS1509</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>健身房</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>18</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2346,43 +2390,44 @@
           <t>15200002.064</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>xkp01050020</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>CLS1509</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>健身房</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>18</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2394,43 +2439,44 @@
           <t>15200002.065</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>xkp01230344</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>CLS1509</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>健身房</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>18</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2442,43 +2488,44 @@
           <t>15200002.066</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
         <is>
           <t>体育与健康2</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>xkp01230325</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>CLS1509</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>健身房</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>18</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2492,39 +2539,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>商务英语</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>xkp01020047</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>CLS1007</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>2104</v>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CLS1004</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>304</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>第3-4节</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>7</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>第3-5节</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2538,39 +2590,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>商务英语</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>xkp01020047</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>CLS1007</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>2104</v>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CLS1004</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>304</v>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>第5-7节</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2579,44 +2636,49 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>110000320.001</t>
+          <t>14403009.001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>线性代数b</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>xkp01040118</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>CLS1021</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>501</v>
-      </c>
-      <c r="G46" t="inlineStr">
+          <t>商务英语</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>xkp01020047</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CLS1004</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>304</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>6</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2625,44 +2687,49 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>110000320.001</t>
+          <t>14403009.001</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>线性代数b</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>xkp01040118</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>CLS1021</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>501</v>
-      </c>
-      <c r="G47" t="inlineStr">
+          <t>商务英语</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>xkp01020047</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CLS1004</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>304</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2671,44 +2738,49 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>110000460.001</t>
+          <t>110000320.001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>xkp01040055</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>CLS1022</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>401</v>
-      </c>
-      <c r="G48" t="inlineStr">
+          <t>线性代数b</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>xkp01040118</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>8</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CLS1021</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>501</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>第1-4节</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>13</v>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2717,44 +2789,49 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>110000460.001</t>
+          <t>110000320.001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>xkp01040055</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>CLS1022</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>401</v>
-      </c>
-      <c r="G49" t="inlineStr">
+          <t>线性代数b</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>xkp01040118</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>CLS1021</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>501</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>第1-4节</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>13</v>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2763,44 +2840,49 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>110000460.002</t>
+          <t>110000320.001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>xkp01040040</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>CLS1023</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>201</v>
-      </c>
-      <c r="G50" t="inlineStr">
+          <t>线性代数b</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>xkp01040118</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CLS1021</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>501</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>13</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2809,44 +2891,49 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>110000460.002</t>
+          <t>110000320.001</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>xkp01040040</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>CLS1023</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>201</v>
-      </c>
-      <c r="G51" t="inlineStr">
+          <t>线性代数b</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>xkp01040118</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CLS1021</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>501</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>13</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2855,44 +2942,49 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>110000460.003</t>
+          <t>110000460.001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>高等数学b-2</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>xkp01230259</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>CLS1026</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>104</v>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>xkp01040055</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>8</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CLS1022</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>401</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>第1-4节</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>13</v>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" t="n">
+        <v>9</v>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2901,44 +2993,49 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>110000460.003</t>
+          <t>110000460.001</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>高等数学b-2</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>xkp01230259</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>CLS1026</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>104</v>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>xkp01040055</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>8</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CLS1022</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>401</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>第1-4节</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>13</v>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" t="n">
+        <v>9</v>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2947,44 +3044,49 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>110000460.004</t>
+          <t>110000460.001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>高等数学b-2</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>xkp01040074</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>CLS1029</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>301</v>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>xkp01040055</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CLS1016</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>2403</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>13</v>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2993,44 +3095,49 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>110000460.004</t>
+          <t>110000460.001</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>高等数学b-2</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>xkp01040074</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>CLS1029</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>301</v>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>xkp01040055</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CLS1016</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>2403</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>13</v>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3039,44 +3146,49 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>110000460.005</t>
+          <t>110000460.002</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>高等数学b-2</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>xkp01040071</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>CLS1038</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>xkp01040040</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CLS1023</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
         <v>201</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>第1-4节</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>13</v>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" t="n">
+        <v>9</v>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3085,44 +3197,49 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>110000460.005</t>
+          <t>110000460.002</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>高等数学b-2</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>xkp01040071</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>CLS1038</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>xkp01040040</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>8</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CLS1023</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
         <v>201</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>第1-4节</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>13</v>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" t="n">
+        <v>9</v>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3131,44 +3248,49 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>110000460.006</t>
+          <t>110000460.002</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>高等数学b-2</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>xkp01230481</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>xkp01040040</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
         <v>6</v>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>CLS1040</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>201</v>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CLS1021</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>501</v>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>第1-3节</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>16</v>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" t="n">
+        <v>4</v>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3177,44 +3299,49 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>110000460.006</t>
+          <t>110000460.002</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>高等数学b-2</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>xkp01230481</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>xkp01040040</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
         <v>6</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>CLS1040</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>201</v>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CLS1021</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>501</v>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>第1-3节</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>16</v>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3223,44 +3350,49 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>110000480.001</t>
+          <t>110000460.003</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>高等数学c-2</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>xkp01040094</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>CLS1076</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>401</v>
-      </c>
-      <c r="G60" t="inlineStr">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>xkp01230259</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>8</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CLS1026</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>104</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>13</v>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>9</v>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3269,44 +3401,49 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>110000480.001</t>
+          <t>110000460.003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>高等数学c-2</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>xkp01040094</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>6</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>CLS1076</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>401</v>
-      </c>
-      <c r="G61" t="inlineStr">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>xkp01230259</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>8</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CLS1026</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>104</v>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>13</v>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>9</v>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3315,44 +3452,49 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>110000480.002</t>
+          <t>110000460.003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>高等数学c-2</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>xkp01040092</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>xkp01230259</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
         <v>6</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>CLS1081</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>2302</v>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CLS1022</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>401</v>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>第1-3节</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>13</v>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" t="n">
+        <v>4</v>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3361,44 +3503,49 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>110000480.002</t>
+          <t>110000460.003</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>高等数学c-2</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>xkp01040092</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>xkp01230259</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
         <v>6</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>CLS1081</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>2302</v>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CLS1022</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>401</v>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>第1-3节</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>13</v>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3407,44 +3554,49 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>110000640.017</t>
+          <t>110000460.004</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>概率论与数理统计</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>xkp01200508</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>CLS1043</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>2402</v>
-      </c>
-      <c r="G64" t="inlineStr">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>xkp01040074</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>8</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CLS1029</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>301</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I64" t="n">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
         <v>9</v>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3453,44 +3605,49 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>110000640.017</t>
+          <t>110000460.004</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>概率论与数理统计</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>xkp01200508</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>CLS1043</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>2402</v>
-      </c>
-      <c r="G65" t="inlineStr">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>xkp01040074</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>8</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>CLS1029</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>301</v>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>第1-4节</t>
         </is>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>9</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3499,44 +3656,49 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>110000670.001</t>
+          <t>110000460.004</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>xkp01040087</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>CLS1185</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>101</v>
-      </c>
-      <c r="G66" t="inlineStr">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>xkp01040074</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>CLS1023</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>201</v>
+      </c>
+      <c r="H66" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I66" t="n">
-        <v>13</v>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>4</v>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3545,44 +3707,49 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>110000670.001</t>
+          <t>110000460.004</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>xkp01040087</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>CLS1185</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>101</v>
-      </c>
-      <c r="G67" t="inlineStr">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>xkp01040074</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>CLS1023</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>201</v>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I67" t="n">
-        <v>13</v>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>4</v>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3591,44 +3758,49 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>110000670.002</t>
+          <t>110000460.005</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>xkp01040064</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>6</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>CLS1441</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>2401</v>
-      </c>
-      <c r="G68" t="inlineStr">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>xkp01040071</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>8</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>CLS1038</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>201</v>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I68" t="n">
-        <v>16</v>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>9</v>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3637,44 +3809,49 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>110000670.002</t>
+          <t>110000460.005</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>xkp01040064</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>6</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>CLS1441</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>2401</v>
-      </c>
-      <c r="G69" t="inlineStr">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>xkp01040071</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>8</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>CLS1038</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>201</v>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
-        <v>16</v>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>9</v>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3683,44 +3860,49 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>130000510.002</t>
+          <t>110000460.005</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>xkp01030027</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>7</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>CLS1093</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1402</v>
-      </c>
-      <c r="G70" t="inlineStr">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>xkp01040071</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CLS1026</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>104</v>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>第1-3节</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>7</v>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" t="n">
+        <v>4</v>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3729,44 +3911,49 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>130000510.002</t>
+          <t>110000460.005</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>xkp01030027</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>7</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>CLS1093</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1402</v>
-      </c>
-      <c r="G71" t="inlineStr">
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>xkp01040071</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>CLS1026</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>104</v>
+      </c>
+      <c r="H71" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I71" t="n">
-        <v>7</v>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>4</v>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3775,44 +3962,49 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>130000510.004</t>
+          <t>110000640.017</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>xkp01030005</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>7</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>CLS1131</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>1303</v>
-      </c>
-      <c r="G72" t="inlineStr">
+          <t>概率论与数理统计</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>xkp01200508</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>2103</v>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3821,44 +4013,49 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>130000510.004</t>
+          <t>110000640.017</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>xkp01030005</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>7</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>CLS1131</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1303</v>
-      </c>
-      <c r="G73" t="inlineStr">
+          <t>概率论与数理统计</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>xkp01200508</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>8</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>2103</v>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>第1-4节</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>7</v>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3867,44 +4064,49 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>130000510.005</t>
+          <t>110000640.017</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>xkp01030037</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>7</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>CLS1133</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1203</v>
-      </c>
-      <c r="G74" t="inlineStr">
+          <t>概率论与数理统计</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>xkp01200508</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>CLS1040</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>201</v>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>第1-3节</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="J74" t="n">
+        <v>8</v>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3913,44 +4115,49 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>130000510.005</t>
+          <t>110000640.017</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>xkp01030037</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>7</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>CLS1133</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>1203</v>
-      </c>
-      <c r="G75" t="inlineStr">
+          <t>概率论与数理统计</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>xkp01200508</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>CLS1040</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>201</v>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>7</v>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>8</v>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3959,44 +4166,49 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>130000510.006</t>
+          <t>110000670.001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>xkp01170071</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>7</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>CLS1139</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>1302</v>
-      </c>
-      <c r="G76" t="inlineStr">
+          <t>高等数学a-2</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>xkp01040087</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>8</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>CLS1185</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>101</v>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>7</v>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>9</v>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4005,44 +4217,49 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>130000510.006</t>
+          <t>110000670.001</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>xkp01170071</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>7</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>CLS1139</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>1302</v>
-      </c>
-      <c r="G77" t="inlineStr">
+          <t>高等数学a-2</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>xkp01040087</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>8</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>CLS1185</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>101</v>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>第1-4节</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>7</v>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77" t="n">
+        <v>9</v>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4051,44 +4268,49 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>130000510.007</t>
+          <t>110000670.001</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>xkp01030033</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>7</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>CLS1166</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>1102</v>
-      </c>
-      <c r="G78" t="inlineStr">
+          <t>高等数学a-2</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>xkp01040087</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>CLS1185</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>101</v>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>第1-3节</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="J78" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4097,44 +4319,49 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>130000510.007</t>
+          <t>110000670.001</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>xkp01030033</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>7</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>CLS1166</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>1102</v>
-      </c>
-      <c r="G79" t="inlineStr">
+          <t>高等数学a-2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>xkp01040087</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CLS1185</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>101</v>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>7</v>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>4</v>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4143,44 +4370,49 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>130000510.008</t>
+          <t>14403010.001</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>xkp01030050</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>7</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>CLS1182</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1206</v>
-      </c>
-      <c r="G80" t="inlineStr">
+          <t>国际贸易实务</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>xkp01230713</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>CLS1003</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>305</v>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>7</v>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>第7-9节</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4189,44 +4421,49 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>130000510.008</t>
+          <t>14403010.001</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>xkp01030050</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>7</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>CLS1182</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>1206</v>
-      </c>
-      <c r="G81" t="inlineStr">
+          <t>国际贸易实务</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>xkp01230713</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CLS1003</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>305</v>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>7</v>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>第9-11节</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4235,44 +4472,49 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>130000510.009</t>
+          <t>14403010.001</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>xkp01030098</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>7</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>CLS1188</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>203</v>
-      </c>
-      <c r="G82" t="inlineStr">
+          <t>国际贸易实务</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>xkp01230713</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>CLS1004</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>304</v>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>7</v>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4281,44 +4523,49 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>130000510.009</t>
+          <t>14403010.001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>xkp01030098</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>7</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>CLS1188</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>203</v>
-      </c>
-      <c r="G83" t="inlineStr">
+          <t>国际贸易实务</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>xkp01230713</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>CLS1004</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>304</v>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>7</v>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4327,44 +4574,49 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>130000510.010</t>
+          <t>17716055.001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>xkp01030018</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>7</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>CLS1189</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>3101</v>
-      </c>
-      <c r="G84" t="inlineStr">
+          <t>短视频平台运营与用户增长</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>xkp01090132</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>2104</v>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>第1-3节</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>7</v>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="J84" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4373,44 +4625,49 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>130000510.010</t>
+          <t>17716055.001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>xkp01030018</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>7</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>CLS1189</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>3101</v>
-      </c>
-      <c r="G85" t="inlineStr">
+          <t>短视频平台运营与用户增长</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>xkp01090132</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>2104</v>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>7</v>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>4</v>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4419,44 +4676,49 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>14403010.001</t>
+          <t>17716055.001</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>国际贸易实务</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>xkp01230713</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>CLS1004</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>304</v>
-      </c>
-      <c r="G86" t="inlineStr">
+          <t>短视频平台运营与用户增长</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>xkp01090132</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>4</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>2103</v>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t>周六</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>第5-7节</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>6</v>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>2</v>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4465,228 +4727,49 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>14403010.001</t>
+          <t>17716055.001</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>国际贸易实务</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>xkp01230713</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>CLS1004</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>304</v>
-      </c>
-      <c r="G87" t="inlineStr">
+          <t>短视频平台运营与用户增长</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>xkp01090132</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>2103</v>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>第9-11节</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>6</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>17716055.001</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>短视频平台运营与用户增长</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>xkp01090132</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>CLS1008</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>2106</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>6</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>17716055.001</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>短视频平台运营与用户增长</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>xkp01090132</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>CLS1008</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>2106</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>周日</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>第1-3节</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>6</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>110010321.001</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>高等代数2</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>xkp01040124</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>8</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>CLS1010</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>2205</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>周六</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>13</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>110010321.001</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>高等代数2</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>xkp01040124</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>8</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>CLS1010</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>2205</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>周日</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>第1-4节</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>13</v>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>B</t>
         </is>

--- a/排课结果/特殊要求放宽排入明细.xlsx
+++ b/排课结果/特殊要求放宽排入明细.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3962,34 +3962,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>110000640.017</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>110000460.006</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>概率论与数理统计</t>
+          <t>高等数学b-2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>xkp01200508</t>
+          <t>xkp01230481</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CLS1006</t>
+          <t>CLS1040</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2103</v>
+        <v>201</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3998,49 +3994,45 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>第1-4节</t>
+          <t>第1-3节</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>110000640.017</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>110000460.006</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>概率论与数理统计</t>
+          <t>高等数学b-2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>xkp01200508</t>
+          <t>xkp01230481</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CLS1006</t>
+          <t>CLS1040</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>2103</v>
+        <v>201</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4049,37 +4041,33 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>第1-4节</t>
+          <t>第1-3节</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>110000640.017</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>FB</t>
-        </is>
-      </c>
+          <t>110000480.001</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>概率论与数理统计</t>
+          <t>高等数学c-2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>xkp01200508</t>
+          <t>xkp01040094</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -4087,11 +4075,11 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CLS1040</t>
+          <t>CLS1076</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4104,33 +4092,29 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>110000640.017</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>FB</t>
-        </is>
-      </c>
+          <t>110000480.001</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>概率论与数理统计</t>
+          <t>高等数学c-2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>xkp01200508</t>
+          <t>xkp01040094</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -4138,11 +4122,11 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CLS1040</t>
+          <t>CLS1076</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4155,45 +4139,41 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>110000670.001</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>110000480.002</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>高等数学c-2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>xkp01040087</t>
+          <t>xkp01040092</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CLS1185</t>
+          <t>CLS1081</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>101</v>
+        <v>2302</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -4202,49 +4182,45 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>第1-4节</t>
+          <t>第1-3节</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>110000670.001</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
+          <t>110000480.002</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>高等数学c-2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>xkp01040087</t>
+          <t>xkp01040092</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CLS1185</t>
+          <t>CLS1081</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>101</v>
+        <v>2302</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4253,49 +4229,49 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>第1-4节</t>
+          <t>第1-3节</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>110000670.001</t>
+          <t>110000640.017</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>概率论与数理统计</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>xkp01040087</t>
+          <t>xkp01200508</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CLS1185</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>101</v>
+        <v>2103</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -4304,11 +4280,11 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>第1-3节</t>
+          <t>第1-4节</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4319,34 +4295,34 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>110000670.001</t>
+          <t>110000640.017</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>概率论与数理统计</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>xkp01040087</t>
+          <t>xkp01200508</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CLS1185</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>101</v>
+        <v>2103</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -4355,11 +4331,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>第1-3节</t>
+          <t>第1-4节</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4370,22 +4346,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>14403010.001</t>
+          <t>110000640.017</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>国际贸易实务</t>
+          <t>概率论与数理统计</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>xkp01230713</t>
+          <t>xkp01200508</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -4393,11 +4369,11 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CLS1003</t>
+          <t>CLS1043</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>305</v>
+        <v>2402</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -4406,11 +4382,11 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>第7-9节</t>
+          <t>第1-3节</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4421,22 +4397,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>14403010.001</t>
+          <t>110000640.017</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>国际贸易实务</t>
+          <t>概率论与数理统计</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>xkp01230713</t>
+          <t>xkp01200508</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -4444,11 +4420,11 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CLS1003</t>
+          <t>CLS1043</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>305</v>
+        <v>2402</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -4457,11 +4433,11 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>第9-11节</t>
+          <t>第1-3节</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4472,34 +4448,34 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>14403010.001</t>
+          <t>110000670.001</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>国际贸易实务</t>
+          <t>高等数学a-2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>xkp01230713</t>
+          <t>xkp01040087</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1185</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>304</v>
+        <v>101</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -4508,11 +4484,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第1-4节</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4523,34 +4499,34 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>14403010.001</t>
+          <t>110000670.001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>国际贸易实务</t>
+          <t>高等数学a-2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>xkp01230713</t>
+          <t>xkp01040087</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1185</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>304</v>
+        <v>101</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -4559,11 +4535,11 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-4节</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4574,22 +4550,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>17716055.001</t>
+          <t>110000670.001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>短视频平台运营与用户增长</t>
+          <t>高等数学a-2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>xkp01090132</t>
+          <t>xkp01040087</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -4597,11 +4573,11 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CLS1007</t>
+          <t>CLS1185</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>2104</v>
+        <v>101</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -4625,22 +4601,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>17716055.001</t>
+          <t>110000670.001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>短视频平台运营与用户增长</t>
+          <t>高等数学a-2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>xkp01090132</t>
+          <t>xkp01040087</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -4648,11 +4624,11 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CLS1007</t>
+          <t>CLS1185</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2104</v>
+        <v>101</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -4676,34 +4652,30 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>17716055.001</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>FB</t>
-        </is>
-      </c>
+          <t>110000670.002</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>短视频平台运营与用户增长</t>
+          <t>高等数学a-2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>xkp01090132</t>
+          <t>xkp01040064</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CLS1006</t>
+          <t>CLS1441</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>2103</v>
+        <v>2401</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -4712,66 +4684,1410 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第1-3节</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>110000670.002</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>高等数学a-2</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>xkp01040064</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CLS1441</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>2401</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>16</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>130000510.002</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>xkp01030027</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>7</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CLS1093</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1402</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>7</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>130000510.002</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>xkp01030027</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>7</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>CLS1093</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>1402</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>130000510.004</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>xkp01030005</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>7</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CLS1131</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1303</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>7</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>130000510.004</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>xkp01030005</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>7</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CLS1131</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1303</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>7</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>130000510.005</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>xkp01030037</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>7</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CLS1133</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1203</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>7</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>130000510.005</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>xkp01030037</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>7</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>CLS1133</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1203</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>7</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>130000510.006</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>xkp01170071</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>7</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>CLS1139</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>1302</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>7</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>130000510.006</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>xkp01170071</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>7</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>CLS1139</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1302</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>7</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>130000510.007</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>xkp01030033</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>7</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CLS1166</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1102</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>7</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>130000510.007</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>xkp01030033</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>7</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>CLS1166</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1102</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>7</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>130000510.008</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>xkp01030050</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>7</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>CLS1182</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>1206</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>7</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>130000510.008</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>xkp01030050</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>7</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>CLS1182</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>1206</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>7</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>130000510.009</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>xkp01030098</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>7</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>CLS1188</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>203</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>7</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>130000510.009</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>xkp01030098</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>7</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>CLS1188</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>203</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>7</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>130000510.010</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>xkp01030018</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>7</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>CLS1189</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>3101</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>7</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>130000510.010</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>xkp01030018</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>7</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>CLS1189</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>3101</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>7</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>14403010.001</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>国际贸易实务</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>xkp01230713</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>CLS1003</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>305</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>第7-9节</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>4</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>14403010.001</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>国际贸易实务</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>xkp01230713</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>CLS1003</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>305</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>第9-11节</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>4</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>14403010.001</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>国际贸易实务</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>xkp01230713</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>CLS1004</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>304</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>2</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>14403010.001</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>国际贸易实务</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>xkp01230713</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>CLS1004</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>304</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>15ALT016.003</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>队田径业余队</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>xkp01050075</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>CLS1278</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>2303</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>15</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>15ALT016.003</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>队田径业余队</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>xkp01050075</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>CLS1278</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>2303</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>第9-11节</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>15</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>17716055.001</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>短视频平台运营与用户增长</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>xkp01090132</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>2104</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>4</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>17716055.001</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>短视频平台运营与用户增长</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>xkp01090132</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>2104</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>第1-3节</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>4</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>17716055.001</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>短视频平台运营与用户增长</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>xkp01090132</t>
         </is>
       </c>
-      <c r="E87" t="n">
+      <c r="E112" t="n">
         <v>4</v>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>CLS1006</t>
         </is>
       </c>
-      <c r="G87" t="n">
+      <c r="G112" t="n">
         <v>2103</v>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>2</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>17716055.001</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>短视频平台运营与用户增长</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>xkp01090132</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>4</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>2103</v>
+      </c>
+      <c r="H113" t="inlineStr">
         <is>
           <t>周日</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>第1-2节</t>
         </is>
       </c>
-      <c r="J87" t="n">
+      <c r="J113" t="n">
         <v>2</v>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>110010321.001</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>高等代数2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>xkp01040124</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>8</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>CLS1010</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>2205</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>13</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>110010321.001</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>高等代数2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>xkp01040124</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>8</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>CLS1010</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>2205</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>第1-4节</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>13</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
